--- a/data/VMP/20250211/Level0/Logbook_Zug_20250211.xlsx
+++ b/data/VMP/20250211/Level0/Logbook_Zug_20250211.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="201" documentId="13_ncr:1_{F97EAE30-667A-4A71-BFDC-08A402DAEF65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68E029C2-20F8-48A3-802B-5B0DFAE4D7EE}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Logbook_Zug" sheetId="1" r:id="rId1"/>
@@ -404,7 +404,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -546,36 +546,6 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -659,12 +629,6 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -972,7 +936,7 @@
     <col min="1" max="2" width="10.140625" style="2" customWidth="1"/>
     <col min="3" max="3" width="17.7109375" style="2" customWidth="1"/>
     <col min="4" max="4" width="13.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17" style="53" customWidth="1"/>
+    <col min="5" max="5" width="17" style="10" customWidth="1"/>
     <col min="6" max="6" width="19.5703125" style="5" customWidth="1"/>
     <col min="7" max="7" width="14.5703125" style="10" customWidth="1"/>
     <col min="8" max="8" width="20.5703125" style="5" customWidth="1"/>
@@ -1004,7 +968,7 @@
       <c r="D1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="54" t="s">
+      <c r="E1" s="7" t="s">
         <v>14</v>
       </c>
       <c r="F1" s="7" t="s">
@@ -1084,7 +1048,7 @@
       <c r="D2" s="33">
         <v>45429</v>
       </c>
-      <c r="E2" s="55">
+      <c r="E2" s="32">
         <v>20</v>
       </c>
       <c r="F2" s="34">
@@ -1162,7 +1126,7 @@
       <c r="D3" s="41">
         <v>45699</v>
       </c>
-      <c r="E3" s="56">
+      <c r="E3" s="40">
         <v>11</v>
       </c>
       <c r="F3" s="42">
@@ -1232,7 +1196,7 @@
       <c r="D4" s="13">
         <v>45699</v>
       </c>
-      <c r="E4" s="57">
+      <c r="E4" s="12">
         <v>11</v>
       </c>
       <c r="F4" s="14">
@@ -1300,7 +1264,7 @@
       <c r="D5" s="20">
         <v>45699</v>
       </c>
-      <c r="E5" s="58">
+      <c r="E5" s="19">
         <v>12</v>
       </c>
       <c r="F5" s="19">
@@ -1364,7 +1328,7 @@
       <c r="B6" s="22"/>
       <c r="C6" s="22"/>
       <c r="D6" s="23"/>
-      <c r="E6" s="59"/>
+      <c r="E6" s="22"/>
       <c r="F6" s="22"/>
       <c r="G6" s="22"/>
       <c r="H6" s="22"/>
@@ -1396,7 +1360,7 @@
       <c r="B7" s="25"/>
       <c r="C7" s="25"/>
       <c r="D7" s="26"/>
-      <c r="E7" s="60"/>
+      <c r="E7" s="25"/>
       <c r="F7" s="25"/>
       <c r="G7" s="25"/>
       <c r="H7" s="25"/>
@@ -1434,7 +1398,7 @@
       <c r="D8" s="50">
         <v>45699</v>
       </c>
-      <c r="E8" s="61">
+      <c r="E8" s="45">
         <v>13</v>
       </c>
       <c r="F8" s="45">
@@ -1502,7 +1466,7 @@
       <c r="D9" s="29">
         <v>45699</v>
       </c>
-      <c r="E9" s="62">
+      <c r="E9" s="28">
         <v>13</v>
       </c>
       <c r="F9" s="28">
@@ -1560,87 +1524,87 @@
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A10" s="63" t="s">
+      <c r="A10" s="53" t="s">
         <v>42</v>
       </c>
-      <c r="B10" s="63">
+      <c r="B10" s="53">
         <v>1</v>
       </c>
-      <c r="C10" s="63" t="s">
+      <c r="C10" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="64">
+      <c r="D10" s="54">
         <v>45699</v>
       </c>
-      <c r="E10" s="91">
+      <c r="E10" s="57">
         <v>14</v>
       </c>
-      <c r="F10" s="67">
+      <c r="F10" s="57">
         <v>40</v>
       </c>
-      <c r="G10" s="67">
+      <c r="G10" s="57">
         <v>15</v>
       </c>
-      <c r="H10" s="67">
+      <c r="H10" s="57">
         <v>40</v>
       </c>
-      <c r="I10" s="65"/>
-      <c r="J10" s="65"/>
-      <c r="K10" s="65"/>
-      <c r="L10" s="65"/>
-      <c r="M10" s="66">
+      <c r="I10" s="55"/>
+      <c r="J10" s="55"/>
+      <c r="K10" s="55"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="56">
         <v>680006</v>
       </c>
-      <c r="N10" s="66">
+      <c r="N10" s="56">
         <v>218754</v>
       </c>
-      <c r="O10" s="63" t="s">
+      <c r="O10" s="53" t="s">
         <v>55</v>
       </c>
-      <c r="P10" s="63"/>
-      <c r="Q10" s="63" t="s">
-        <v>28</v>
-      </c>
-      <c r="R10" s="63">
-        <v>28</v>
-      </c>
-      <c r="S10" s="63">
+      <c r="P10" s="53"/>
+      <c r="Q10" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="R10" s="53">
+        <v>28</v>
+      </c>
+      <c r="S10" s="53">
         <v>1699</v>
       </c>
-      <c r="T10" s="63">
+      <c r="T10" s="53">
         <v>1704</v>
       </c>
-      <c r="U10" s="63">
+      <c r="U10" s="53">
         <v>2020</v>
       </c>
-      <c r="V10" s="63">
+      <c r="V10" s="53">
         <v>2080</v>
       </c>
-      <c r="W10" s="63" t="s">
-        <v>34</v>
-      </c>
-      <c r="X10" s="63" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y10" s="67"/>
-      <c r="Z10" s="65" t="s">
+      <c r="W10" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="X10" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y10" s="57"/>
+      <c r="Z10" s="55" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A11" s="68" t="s">
+      <c r="A11" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="68">
+      <c r="B11" s="58">
         <v>1</v>
       </c>
-      <c r="C11" s="68" t="s">
+      <c r="C11" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="69">
+      <c r="D11" s="59">
         <v>45699</v>
       </c>
-      <c r="E11" s="57">
+      <c r="E11" s="12">
         <v>15</v>
       </c>
       <c r="F11" s="12">
@@ -1652,111 +1616,111 @@
       <c r="H11" s="12">
         <v>0</v>
       </c>
-      <c r="I11" s="70"/>
-      <c r="J11" s="70"/>
-      <c r="K11" s="70"/>
-      <c r="L11" s="70"/>
-      <c r="M11" s="71">
+      <c r="I11" s="60"/>
+      <c r="J11" s="60"/>
+      <c r="K11" s="60"/>
+      <c r="L11" s="60"/>
+      <c r="M11" s="61">
         <v>679991</v>
       </c>
-      <c r="N11" s="71">
+      <c r="N11" s="61">
         <v>218745</v>
       </c>
-      <c r="O11" s="68" t="s">
+      <c r="O11" s="58" t="s">
         <v>57</v>
       </c>
-      <c r="P11" s="68"/>
-      <c r="Q11" s="68" t="s">
-        <v>28</v>
-      </c>
-      <c r="R11" s="68">
-        <v>28</v>
-      </c>
-      <c r="S11" s="68">
+      <c r="P11" s="58"/>
+      <c r="Q11" s="58" t="s">
+        <v>28</v>
+      </c>
+      <c r="R11" s="58">
+        <v>28</v>
+      </c>
+      <c r="S11" s="58">
         <v>1699</v>
       </c>
-      <c r="T11" s="68">
+      <c r="T11" s="58">
         <v>1704</v>
       </c>
-      <c r="U11" s="68">
+      <c r="U11" s="58">
         <v>2020</v>
       </c>
-      <c r="V11" s="68">
+      <c r="V11" s="58">
         <v>2080</v>
       </c>
-      <c r="W11" s="68" t="s">
-        <v>34</v>
-      </c>
-      <c r="X11" s="68" t="s">
+      <c r="W11" s="58" t="s">
+        <v>34</v>
+      </c>
+      <c r="X11" s="58" t="s">
         <v>34</v>
       </c>
       <c r="Y11" s="12"/>
-      <c r="Z11" s="70" t="s">
+      <c r="Z11" s="60" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A12" s="72" t="s">
+      <c r="A12" s="62" t="s">
         <v>44</v>
       </c>
-      <c r="B12" s="73"/>
-      <c r="C12" s="73"/>
-      <c r="D12" s="74"/>
-      <c r="E12" s="58"/>
+      <c r="B12" s="63"/>
+      <c r="C12" s="63"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="19"/>
       <c r="F12" s="19"/>
       <c r="G12" s="19"/>
       <c r="H12" s="19"/>
-      <c r="I12" s="75"/>
-      <c r="J12" s="75"/>
-      <c r="K12" s="75"/>
-      <c r="L12" s="75"/>
-      <c r="M12" s="76"/>
-      <c r="N12" s="76"/>
-      <c r="O12" s="73"/>
-      <c r="P12" s="73"/>
-      <c r="Q12" s="73" t="s">
-        <v>28</v>
-      </c>
-      <c r="R12" s="73">
-        <v>28</v>
-      </c>
-      <c r="S12" s="73">
+      <c r="I12" s="65"/>
+      <c r="J12" s="65"/>
+      <c r="K12" s="65"/>
+      <c r="L12" s="65"/>
+      <c r="M12" s="66"/>
+      <c r="N12" s="66"/>
+      <c r="O12" s="63"/>
+      <c r="P12" s="63"/>
+      <c r="Q12" s="63" t="s">
+        <v>28</v>
+      </c>
+      <c r="R12" s="63">
+        <v>28</v>
+      </c>
+      <c r="S12" s="63">
         <v>1699</v>
       </c>
-      <c r="T12" s="73">
+      <c r="T12" s="63">
         <v>1704</v>
       </c>
-      <c r="U12" s="73">
+      <c r="U12" s="63">
         <v>2020</v>
       </c>
-      <c r="V12" s="73">
+      <c r="V12" s="63">
         <v>2080</v>
       </c>
-      <c r="W12" s="73" t="s">
-        <v>34</v>
-      </c>
-      <c r="X12" s="73" t="s">
+      <c r="W12" s="63" t="s">
+        <v>34</v>
+      </c>
+      <c r="X12" s="63" t="s">
         <v>34</v>
       </c>
       <c r="Y12" s="19"/>
-      <c r="Z12" s="77" t="s">
+      <c r="Z12" s="67" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A13" s="78" t="s">
+      <c r="A13" s="68" t="s">
         <v>45</v>
       </c>
-      <c r="B13" s="78">
+      <c r="B13" s="68">
         <v>1</v>
       </c>
-      <c r="C13" s="78" t="s">
+      <c r="C13" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="79">
+      <c r="D13" s="69">
         <v>45699</v>
       </c>
-      <c r="E13" s="59">
+      <c r="E13" s="22">
         <v>15</v>
       </c>
       <c r="F13" s="22">
@@ -1768,63 +1732,63 @@
       <c r="H13" s="22">
         <v>30</v>
       </c>
-      <c r="I13" s="80"/>
-      <c r="J13" s="80"/>
-      <c r="K13" s="80"/>
-      <c r="L13" s="80"/>
-      <c r="M13" s="81">
+      <c r="I13" s="70"/>
+      <c r="J13" s="70"/>
+      <c r="K13" s="70"/>
+      <c r="L13" s="70"/>
+      <c r="M13" s="71">
         <v>680015</v>
       </c>
-      <c r="N13" s="81">
+      <c r="N13" s="71">
         <v>218745</v>
       </c>
-      <c r="O13" s="78" t="s">
+      <c r="O13" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="P13" s="78"/>
-      <c r="Q13" s="78" t="s">
-        <v>28</v>
-      </c>
-      <c r="R13" s="78">
-        <v>28</v>
-      </c>
-      <c r="S13" s="78">
+      <c r="P13" s="68"/>
+      <c r="Q13" s="68" t="s">
+        <v>28</v>
+      </c>
+      <c r="R13" s="68">
+        <v>28</v>
+      </c>
+      <c r="S13" s="68">
         <v>1699</v>
       </c>
-      <c r="T13" s="78">
+      <c r="T13" s="68">
         <v>1704</v>
       </c>
-      <c r="U13" s="78">
+      <c r="U13" s="68">
         <v>2020</v>
       </c>
-      <c r="V13" s="78">
+      <c r="V13" s="68">
         <v>2080</v>
       </c>
-      <c r="W13" s="78" t="s">
-        <v>34</v>
-      </c>
-      <c r="X13" s="78" t="s">
+      <c r="W13" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="X13" s="68" t="s">
         <v>34</v>
       </c>
       <c r="Y13" s="22"/>
-      <c r="Z13" s="80" t="s">
+      <c r="Z13" s="70" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="82" t="s">
+      <c r="A14" s="72" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="82">
+      <c r="B14" s="72">
         <v>1</v>
       </c>
-      <c r="C14" s="82" t="s">
+      <c r="C14" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="83">
+      <c r="D14" s="73">
         <v>45699</v>
       </c>
-      <c r="E14" s="60">
+      <c r="E14" s="25">
         <v>16</v>
       </c>
       <c r="F14" s="25">
@@ -1836,114 +1800,114 @@
       <c r="H14" s="25">
         <v>3</v>
       </c>
-      <c r="I14" s="84"/>
-      <c r="J14" s="84"/>
-      <c r="K14" s="84"/>
-      <c r="L14" s="84"/>
-      <c r="M14" s="85">
+      <c r="I14" s="74"/>
+      <c r="J14" s="74"/>
+      <c r="K14" s="74"/>
+      <c r="L14" s="74"/>
+      <c r="M14" s="75">
         <v>680014</v>
       </c>
-      <c r="N14" s="85">
+      <c r="N14" s="75">
         <v>218751</v>
       </c>
-      <c r="O14" s="82" t="s">
+      <c r="O14" s="72" t="s">
         <v>59</v>
       </c>
-      <c r="P14" s="82"/>
-      <c r="Q14" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="R14" s="82">
-        <v>28</v>
-      </c>
-      <c r="S14" s="82">
+      <c r="P14" s="72"/>
+      <c r="Q14" s="72" t="s">
+        <v>28</v>
+      </c>
+      <c r="R14" s="72">
+        <v>28</v>
+      </c>
+      <c r="S14" s="72">
         <v>1699</v>
       </c>
-      <c r="T14" s="82">
+      <c r="T14" s="72">
         <v>1704</v>
       </c>
-      <c r="U14" s="82">
+      <c r="U14" s="72">
         <v>2020</v>
       </c>
-      <c r="V14" s="82">
+      <c r="V14" s="72">
         <v>2080</v>
       </c>
-      <c r="W14" s="82" t="s">
-        <v>34</v>
-      </c>
-      <c r="X14" s="82" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y14" s="82"/>
-      <c r="Z14" s="86" t="s">
+      <c r="W14" s="72" t="s">
+        <v>34</v>
+      </c>
+      <c r="X14" s="72" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y14" s="72"/>
+      <c r="Z14" s="76" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A15" s="87" t="s">
+      <c r="A15" s="77" t="s">
         <v>47</v>
       </c>
-      <c r="B15" s="87">
+      <c r="B15" s="77">
         <v>1</v>
       </c>
-      <c r="C15" s="87" t="s">
+      <c r="C15" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="88">
+      <c r="D15" s="78">
         <v>45699</v>
       </c>
-      <c r="E15" s="92">
+      <c r="E15" s="81">
         <v>16</v>
       </c>
-      <c r="F15" s="93">
+      <c r="F15" s="81">
         <v>30</v>
       </c>
-      <c r="G15" s="93">
+      <c r="G15" s="81">
         <v>17</v>
       </c>
-      <c r="H15" s="93">
+      <c r="H15" s="81">
         <v>30</v>
       </c>
-      <c r="I15" s="89"/>
-      <c r="J15" s="89"/>
-      <c r="K15" s="89"/>
-      <c r="L15" s="89"/>
-      <c r="M15" s="90">
+      <c r="I15" s="79"/>
+      <c r="J15" s="79"/>
+      <c r="K15" s="79"/>
+      <c r="L15" s="79"/>
+      <c r="M15" s="80">
         <v>680406</v>
       </c>
-      <c r="N15" s="90">
+      <c r="N15" s="80">
         <v>216798</v>
       </c>
-      <c r="O15" s="87" t="s">
+      <c r="O15" s="77" t="s">
         <v>60</v>
       </c>
-      <c r="P15" s="87"/>
-      <c r="Q15" s="87" t="s">
-        <v>28</v>
-      </c>
-      <c r="R15" s="87">
-        <v>28</v>
-      </c>
-      <c r="S15" s="87">
+      <c r="P15" s="77"/>
+      <c r="Q15" s="77" t="s">
+        <v>28</v>
+      </c>
+      <c r="R15" s="77">
+        <v>28</v>
+      </c>
+      <c r="S15" s="77">
         <v>1699</v>
       </c>
-      <c r="T15" s="87">
+      <c r="T15" s="77">
         <v>1704</v>
       </c>
-      <c r="U15" s="87">
+      <c r="U15" s="77">
         <v>2020</v>
       </c>
-      <c r="V15" s="87">
+      <c r="V15" s="77">
         <v>2080</v>
       </c>
-      <c r="W15" s="87" t="s">
-        <v>34</v>
-      </c>
-      <c r="X15" s="87" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y15" s="87"/>
-      <c r="Z15" s="89" t="s">
+      <c r="W15" s="77" t="s">
+        <v>34</v>
+      </c>
+      <c r="X15" s="77" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y15" s="77"/>
+      <c r="Z15" s="79" t="s">
         <v>63</v>
       </c>
     </row>
@@ -1952,7 +1916,7 @@
       <c r="L19" s="36"/>
     </row>
     <row r="23" spans="5:12" x14ac:dyDescent="0.25">
-      <c r="E23" s="94"/>
+      <c r="E23" s="82"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/VMP/20250211/Level0/Logbook_Zug_20250211.xlsx
+++ b/data/VMP/20250211/Level0/Logbook_Zug_20250211.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="201" documentId="13_ncr:1_{F97EAE30-667A-4A71-BFDC-08A402DAEF65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68E029C2-20F8-48A3-802B-5B0DFAE4D7EE}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Logbook_Zug" sheetId="1" r:id="rId1"/>
